--- a/data/trans_orig/IP19C03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10161</t>
+          <t>10185</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22453</t>
+          <t>21365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9535</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20818</t>
+          <t>21708</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>23723</t>
+          <t>22986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39258</t>
+          <t>38710</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,52%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53220</t>
+          <t>54308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65512</t>
+          <t>65488</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>71,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>61370</t>
+          <t>60480</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>72653</t>
+          <t>72326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>73,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>118603</t>
+          <t>119151</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134138</t>
+          <t>134875</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,44%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22019</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36260</t>
+          <t>36179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14755</t>
+          <t>14713</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27293</t>
+          <t>28059</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>39841</t>
+          <t>40498</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59500</t>
+          <t>59709</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73801</t>
+          <t>73882</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88042</t>
+          <t>87874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>84338</t>
+          <t>83572</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>96876</t>
+          <t>96918</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162192</t>
+          <t>161983</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181851</t>
+          <t>181194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,73%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10159</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>20644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8239</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18464</t>
+          <t>19163</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20307</t>
+          <t>21135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35258</t>
+          <t>35343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>47996</t>
+          <t>48564</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>58940</t>
+          <t>59049</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59405</t>
+          <t>58706</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>69610</t>
+          <t>69630</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111819</t>
+          <t>111734</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>126770</t>
+          <t>125942</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20459</t>
+          <t>20083</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9898</t>
+          <t>9660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21352</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>21485</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>37894</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,37%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>75530</t>
+          <t>75906</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>87655</t>
+          <t>87505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,69%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>68104</t>
+          <t>68691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>80145</t>
+          <t>80383</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,64%</t>
+          <t>76,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149079</t>
+          <t>148138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165498</t>
+          <t>164547</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>88,45%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61716</t>
+          <t>62455</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87218</t>
+          <t>85858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52195</t>
+          <t>52878</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>76163</t>
+          <t>75264</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>120886</t>
+          <t>119633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152067</t>
+          <t>152819</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>263712</t>
+          <t>265072</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>289214</t>
+          <t>288475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>285568</t>
+          <t>286467</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>309536</t>
+          <t>308853</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,57%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>560594</t>
+          <t>559842</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>591775</t>
+          <t>593028</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,66%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,21%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6671</t>
+          <t>7313</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>16598</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12493</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>24851</t>
+          <t>24751</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21200</t>
+          <t>21203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37987</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56766</t>
+          <t>57320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67247</t>
+          <t>66605</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,8%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>50391</t>
+          <t>50491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62749</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111172</t>
+          <t>111178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127959</t>
+          <t>127956</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23947</t>
+          <t>24474</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>38915</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19771</t>
+          <t>19889</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>34736</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48670</t>
+          <t>48082</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68963</t>
+          <t>68762</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>73406</t>
+          <t>73047</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>87488</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80733</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95507</t>
+          <t>95389</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158277</t>
+          <t>158478</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178570</t>
+          <t>179158</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,84%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8331</t>
+          <t>8680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18450</t>
+          <t>18992</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11814</t>
+          <t>11602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>23846</t>
+          <t>23296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22722</t>
+          <t>22948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38509</t>
+          <t>38946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,25%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>56047</t>
+          <t>55505</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>65817</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>74,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>55907</t>
+          <t>56457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67939</t>
+          <t>68151</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>70,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115741</t>
+          <t>115304</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131528</t>
+          <t>131302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,12%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24187</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4978</t>
+          <t>5205</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14716</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18685</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34988</t>
+          <t>34922</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68790</t>
+          <t>68614</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>81151</t>
+          <t>81169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,28%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81492</t>
+          <t>81585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91323</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154289</t>
+          <t>154355</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170862</t>
+          <t>170592</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,13%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61062</t>
+          <t>60546</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85384</t>
+          <t>84849</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58221</t>
+          <t>59864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>83474</t>
+          <t>83812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126829</t>
+          <t>125795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162877</t>
+          <t>161024</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>267969</t>
+          <t>268504</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>292291</t>
+          <t>292807</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>283100</t>
+          <t>282762</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>308353</t>
+          <t>306710</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>557050</t>
+          <t>558903</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>593098</t>
+          <t>594132</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,53%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10045</t>
+          <t>10410</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21437</t>
+          <t>21869</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18102</t>
+          <t>17702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19948</t>
+          <t>19695</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37301</t>
+          <t>35583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>24,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49404</t>
+          <t>48972</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60796</t>
+          <t>60431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58444</t>
+          <t>58844</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69298</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110086</t>
+          <t>111804</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127439</t>
+          <t>127692</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,64%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29580</t>
+          <t>28922</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18577</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32831</t>
+          <t>32990</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>37658</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56888</t>
+          <t>57514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,65%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77603</t>
+          <t>78261</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91426</t>
+          <t>91648</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>75761</t>
+          <t>75602</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90015</t>
+          <t>90337</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158886</t>
+          <t>158260</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>178116</t>
+          <t>177651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,33%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17963</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11744</t>
+          <t>12086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25072</t>
+          <t>24762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22672</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>57625</t>
+          <t>57110</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67876</t>
+          <t>67588</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,24%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>51791</t>
+          <t>52101</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65119</t>
+          <t>64777</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114033</t>
+          <t>113644</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129779</t>
+          <t>129907</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18774</t>
+          <t>18361</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7248</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>32555</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>90233</t>
+          <t>90646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>101964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88390</t>
+          <t>88003</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>99509</t>
+          <t>99535</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183649</t>
+          <t>183209</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198926</t>
+          <t>198717</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,1%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50723</t>
+          <t>51337</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>73260</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54839</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>79158</t>
+          <t>81047</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>112577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>147795</t>
+          <t>145356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>288675</t>
+          <t>289358</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>311895</t>
+          <t>311281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>289600</t>
+          <t>287711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>313919</t>
+          <t>312918</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>583581</t>
+          <t>586020</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>617418</t>
+          <t>618799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,61%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8773</t>
+          <t>8449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>18821</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5375</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,47 +6624,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>21,86%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>23760</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>15765</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>33308</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>15,33%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>10,17%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>21,49%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>23760</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>16131</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>33296</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>15,33%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>10,41%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>21,48%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>50813</t>
+          <t>50945</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60993</t>
+          <t>61317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66930</t>
+          <t>66615</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79964</t>
+          <t>79874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,47 +6737,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>78,14%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>93,69%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>131255</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>121707</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>139250</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>84,67%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>78,51%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>131255</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>121719</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>138884</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>84,67%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>78,52%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,83%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9066</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41160</t>
+          <t>41103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35244</t>
+          <t>36381</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58634</t>
+          <t>57247</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>92203</t>
+          <t>92235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104667</t>
+          <t>104854</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126216</t>
+          <t>126273</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>145279</t>
+          <t>144366</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>222475</t>
+          <t>223862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>245865</t>
+          <t>244728</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,06%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>19964</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38643</t>
+          <t>39210</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13900</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30283</t>
+          <t>29932</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36765</t>
+          <t>38196</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>62760</t>
+          <t>63035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68312</t>
+          <t>67745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86992</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>89964</t>
+          <t>90315</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106347</t>
+          <t>106663</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164442</t>
+          <t>164167</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>190437</t>
+          <t>189006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,38%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8750</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20842</t>
+          <t>19709</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>9719</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25039</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21515</t>
+          <t>20694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>81470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>92429</t>
+          <t>93141</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86532</t>
+          <t>86939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101327</t>
+          <t>101852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,56%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173739</t>
+          <t>173906</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>191236</t>
+          <t>192057</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,27%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>56430</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84026</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>65330</t>
+          <t>63316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>96364</t>
+          <t>94934</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>126168</t>
+          <t>129528</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169935</t>
+          <t>169743</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>307607</t>
+          <t>308711</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>335203</t>
+          <t>336696</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>388080</t>
+          <t>389510</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>419114</t>
+          <t>421128</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706141</t>
+          <t>706333</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>749908</t>
+          <t>746548</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP19C03-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP19C03-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>14895</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9668</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>21025</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>11,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>25,58%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>15581</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10185</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21365</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10448</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>21463</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>20,59%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>14895</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>9862</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>21708</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,12%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,41%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22986</t>
+          <t>22947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>38710</t>
+          <t>39689</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,52%</t>
+          <t>25,14%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67293</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>61163</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>72520</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>74,42%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>88,24%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>60092</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54308</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>65488</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54210</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>65225</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>79,41%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>86,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>67293</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>60480</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>72326</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>81,88%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119151</t>
+          <t>118172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>134875</t>
+          <t>134914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,46%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>82188</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>75673</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>82188</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>20770</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>14717</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>27971</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>18,61%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,18%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>25,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>28861</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>22187</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36179</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22541</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>37068</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>26,22%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>20,16%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>20770</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>14713</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>28059</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>18,61%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>40498</t>
+          <t>39743</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59709</t>
+          <t>60791</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>90861</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83660</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96914</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>74,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,82%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>81200</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73882</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87874</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72993</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>87520</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>73,78%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>79,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>90861</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83572</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>96918</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>81,39%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>66,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>79,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>161983</t>
+          <t>160901</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>181194</t>
+          <t>181949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111631</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>110061</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111631</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12601</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>8219</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>17877</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>16,18%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>10,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>15125</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>10159</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>20644</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>10582</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>21562</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>21,85%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,68%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12601</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>8239</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>19163</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>16,18%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>21082</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35343</t>
+          <t>35879</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,39%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65268</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>59992</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69650</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>83,82%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77,04%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>89,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>54083</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48564</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>59049</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>47646</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>58626</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>78,15%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>70,17%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>85,32%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65268</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>58706</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69630</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>83,82%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,39%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111734</t>
+          <t>111198</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125942</t>
+          <t>125995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,67%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>77869</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>69208</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>77869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15205</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>10007</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22523</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>16,89%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,01%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>13222</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8484</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>20083</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8395</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>20458</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>13,77%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,84%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>20,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>15205</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>9660</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>21352</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21485</t>
+          <t>20972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37894</t>
+          <t>37872</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>74838</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>67520</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>80036</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>83,11%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>74,99%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>88,89%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>82767</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>75906</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>87505</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>75531</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>87594</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>86,23%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>79,08%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,16%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>74838</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>68691</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>80383</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>83,11%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148138</t>
+          <t>148160</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>164547</t>
+          <t>165060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,63%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>90043</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>95989</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>90043</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>63471</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>52631</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>74619</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72789</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>62455</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>85858</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>60600</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85800</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,74%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,8%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,47%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>63471</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>52878</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>75264</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>17,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119633</t>
+          <t>119807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>152819</t>
+          <t>155465</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>450</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>298260</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>287112</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>309100</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,37%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>412</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>278141</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>265072</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>288475</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>265130</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>290330</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,26%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,53%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,2%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>298260</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>286467</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>308853</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>82,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>559842</t>
+          <t>557196</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>593028</t>
+          <t>592854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,19%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>361731</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>522</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>350930</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>361731</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>18106</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12122</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>24660</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>32,77%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>11363</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7313</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16598</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6604</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>17000</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>15,37%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,45%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>18106</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>12091</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>24751</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>24,06%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21203</t>
+          <t>21804</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>57136</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>50582</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>63120</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>67,23%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,89%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62555</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>57320</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>66605</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>56918</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67314</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>84,63%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>90,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>57136</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>50491</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>63151</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>75,94%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>77,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111178</t>
+          <t>110753</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127956</t>
+          <t>127355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>85,38%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75242</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>73918</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75242</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>27035</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20472</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35342</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,45%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>17,76%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,66%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>31204</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>24474</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38915</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>24407</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39131</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>27,87%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>21,86%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>27035</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19889</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34736</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,45%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48082</t>
+          <t>48557</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>68762</t>
+          <t>69259</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88243</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79936</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>94806</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,55%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,34%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>82,24%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>80758</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>73047</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87488</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72831</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>87555</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,13%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>78,14%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88243</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80542</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>95389</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,55%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158478</t>
+          <t>157981</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>179158</t>
+          <t>178683</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,63%</t>
         </is>
       </c>
     </row>
@@ -3244,52 +3244,52 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
+          <t>115278</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115278</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115278</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
           <t>111962</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>111962</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>111962</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>115278</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>115278</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>115278</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17008</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12044</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>23407</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,1%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>13106</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8680</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18992</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>8222</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>19230</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>17,59%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>25,49%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>17008</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>11602</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>23296</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>21,33%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22948</t>
+          <t>22853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38946</t>
+          <t>38697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62745</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56346</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>67709</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>78,67%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>70,65%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>84,9%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>61391</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>55505</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>65817</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>55267</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>66275</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>82,41%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>74,51%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>88,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>62745</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56457</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>68151</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>78,67%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>115304</t>
+          <t>115553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131302</t>
+          <t>131397</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,18%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79753</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>74497</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>79753</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8971</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4891</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15126</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,32%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>15,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>17272</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>11808</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>24363</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>11764</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>24905</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>18,58%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>26,2%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>8971</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5205</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>14716</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18685</t>
+          <t>18851</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34922</t>
+          <t>34605</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>87330</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>81175</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91410</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,68%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>84,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>75705</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>81169</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>68072</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>81213</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>81,42%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>73,8%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>87330</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>81585</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>91096</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,68%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>154355</t>
+          <t>154672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>170592</t>
+          <t>170426</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,04%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>96301</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>92977</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>96301</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58627</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>83973</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>19,4%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,99%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>72944</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>60546</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>84849</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>62117</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>85259</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>20,64%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>24,01%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>71120</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>59864</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>83812</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>19,4%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>125795</t>
+          <t>127695</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>161024</t>
+          <t>160607</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>419</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>295454</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>282601</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>307947</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>80,6%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>396</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>280409</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>268504</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>292807</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>268094</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>291236</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>79,36%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>75,99%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>419</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>295454</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>282762</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>306710</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>80,6%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>75,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>82,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>558903</t>
+          <t>559320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>594132</t>
+          <t>592232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>82,26%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>366574</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>503</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>353353</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>366574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11752</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>7270</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>18236</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,82%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>15489</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>10410</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>21869</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10639</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>22019</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>21,86%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,7%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>30,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>11752</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>7216</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>17702</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19695</t>
+          <t>19547</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35583</t>
+          <t>35511</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64794</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>58310</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>69276</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,65%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,18%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>90,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>55352</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>48972</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60431</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>48822</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>60202</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>78,14%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>69,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>85,3%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64794</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>58844</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>69330</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,65%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111804</t>
+          <t>111876</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>127692</t>
+          <t>127840</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,74%</t>
         </is>
       </c>
     </row>
@@ -4848,52 +4848,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>76546</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>76546</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>76546</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>70841</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>76546</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>76546</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>76546</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>25040</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18399</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>32796</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>16,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>30,2%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>22019</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15535</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>28922</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>16030</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>29259</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>20,54%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>14,49%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>25040</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18255</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>32990</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>23,06%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57514</t>
+          <t>57080</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>26,45%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>83552</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75796</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>90193</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>83,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>85164</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78261</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>91648</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77924</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>91153</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>79,46%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>85,51%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>83552</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>75602</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>90337</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>76,94%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>85,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158260</t>
+          <t>158694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>177651</t>
+          <t>177774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,39%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108592</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>107183</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>18169</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12657</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>24480</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>16,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>31,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>12100</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8000</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>18478</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>7705</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>18291</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>16,01%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>24,45%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>18169</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>12086</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>24762</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>22530</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>38907</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>58694</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52383</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>64206</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>76,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>68,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>63488</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>57110</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>67588</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57297</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>67883</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>83,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>75,55%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>58694</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>52101</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>64777</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>76,36%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113644</t>
+          <t>113544</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>129907</t>
+          <t>129921</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,22%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>76863</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>75588</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>76863</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>7550</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>18252</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>11,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>17,1%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>12023</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>7043</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>18361</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7507</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>19053</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>11,03%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>16,84%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>12129</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>7222</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18754</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>11,36%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>32555</t>
+          <t>33595</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>94628</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88505</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99207</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>88,64%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>82,9%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>96984</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>90646</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>101964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>89954</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>101500</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>88,97%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,16%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>94628</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>88003</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>99535</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>88,64%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>183209</t>
+          <t>182169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>198717</t>
+          <t>198169</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>106757</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>109007</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>106757</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5994,67 +5994,67 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>67090</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>56471</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>80516</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>18,19%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,83%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
           <t>61631</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>51337</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>73260</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>49923</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>73348</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>17,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,16%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>20,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>67090</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>55840</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>81047</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>112577</t>
+          <t>112503</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>145356</t>
+          <t>146019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>301668</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>288242</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>312287</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>81,81%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>78,17%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>433</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>300987</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>289358</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>311281</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>289270</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>312695</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>83,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>79,8%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>301668</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>287711</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>312918</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>81,81%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,02%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>586020</t>
+          <t>585357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>618799</t>
+          <t>618873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,13%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>84,62%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>368758</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>362618</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>368758</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10234</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5294</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17444</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>13027</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>8449</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18821</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>12,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10733</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5375</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>19316</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23760</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15765</t>
+          <t>16378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33308</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>71223</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64013</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76163</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>78,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>56739</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50945</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>61317</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>87,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74516</t>
+          <t>60754</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66615</t>
+          <t>54962</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79874</t>
+          <t>65656</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>131255</t>
+          <t>131978</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121707</t>
+          <t>122943</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139250</t>
+          <t>139357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>81457</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>69766</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85249</t>
+          <t>74278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>155015</t>
+          <t>155735</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>28491</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>20380</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>38087</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>17,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>12,55%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>14769</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>8879</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21498</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12,99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,81%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>18,9%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30606</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>9160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41103</t>
+          <t>21446</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,56%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>43403</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36381</t>
+          <t>32538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57247</t>
+          <t>54347</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133839</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>124243</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>141950</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>82,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,54%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,45%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>98964</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>92235</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>104854</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>87,01%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>81,1%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,19%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>136770</t>
+          <t>102074</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>126273</t>
+          <t>95540</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>144366</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,44%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>235734</t>
+          <t>235913</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>223862</t>
+          <t>224969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>244728</t>
+          <t>246778</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>88,35%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>162330</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>113733</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>167376</t>
+          <t>116986</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>281109</t>
+          <t>279316</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>20086</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>12579</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>28710</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>17,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>11,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,61%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>27746</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19964</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>39210</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,94%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>36,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>21221</t>
+          <t>25237</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>18312</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29932</t>
+          <t>33683</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>48967</t>
+          <t>45324</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38196</t>
+          <t>34850</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63035</t>
+          <t>56942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>26,54%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>92012</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>83388</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99519</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>82,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>74,39%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>88,78%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>79209</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>67745</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>86991</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>74,06%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>81,33%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>103</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>99026</t>
+          <t>77202</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>90315</t>
+          <t>68756</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>106663</t>
+          <t>84127</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>75,11%</t>
+          <t>67,12%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>178235</t>
+          <t>169213</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>164167</t>
+          <t>157595</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>189006</t>
+          <t>179687</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>78,45%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,19%</t>
+          <t>83,76%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112098</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>142</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>106955</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120247</t>
+          <t>102439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227202</t>
+          <t>214537</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14059</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8373</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21536</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13,36%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,96%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13364</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>8038</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>19709</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,48%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9719</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24632</t>
+          <t>20437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>29593</t>
+          <t>27699</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>20565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>37347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,97%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>87815</t>
+          <t>91150</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81470</t>
+          <t>83673</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>93141</t>
+          <t>96836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>95343</t>
+          <t>88936</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>86939</t>
+          <t>82138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>101852</t>
+          <t>93751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>80,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>183158</t>
+          <t>180085</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>173906</t>
+          <t>170437</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>192057</t>
+          <t>187219</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,1%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>105209</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>101179</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>111571</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>212751</t>
+          <t>207784</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72870</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>58072</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>88226</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,8%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>12,59%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>19,13%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>97</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>68906</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>54937</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>82922</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>14,03%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>78788</t>
+          <t>67312</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>55645</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>94934</t>
+          <t>79711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>147694</t>
+          <t>140182</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129528</t>
+          <t>122944</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169743</t>
+          <t>160070</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>388225</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>372869</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>403023</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>80,87%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>87,41%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>322727</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>308711</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>336696</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>82,41%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>78,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>85,97%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>405656</t>
+          <t>328966</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>389510</t>
+          <t>316567</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>421128</t>
+          <t>340633</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>83,74%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>728382</t>
+          <t>717190</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>706333</t>
+          <t>697302</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>746548</t>
+          <t>734428</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>461095</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>554</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>391633</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>484444</t>
+          <t>396278</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>876076</t>
+          <t>857372</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
